--- a/Storico_Validato_Betting.xlsx
+++ b/Storico_Validato_Betting.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="74">
   <si>
     <t>Campionato</t>
   </si>
@@ -73,13 +73,16 @@
     <t>U/O 2.5</t>
   </si>
   <si>
-    <t>Risultato Reale</t>
-  </si>
-  <si>
-    <t>Esito 1X2</t>
-  </si>
-  <si>
-    <t>Esito U/O 2.5</t>
+    <t>Risultato_Reale</t>
+  </si>
+  <si>
+    <t>Esito_1X2</t>
+  </si>
+  <si>
+    <t>Esito_Risultato_Esatto</t>
+  </si>
+  <si>
+    <t>Esito_U/O_2.5</t>
   </si>
   <si>
     <t>Esito DC+U/O2.5</t>
@@ -223,19 +226,7 @@
     <t>3-1</t>
   </si>
   <si>
-    <t>In Attesa</t>
-  </si>
-  <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>7-1</t>
+    <t>NON ANCORA REALE/DA VALIDARE</t>
   </si>
   <si>
     <t>VINCENTE</t>
@@ -602,10 +593,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W17"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -675,16 +666,19 @@
       <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:24">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -693,69 +687,72 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R2">
         <v>1</v>
       </c>
       <c r="S2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="U2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="V2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="W2" t="s">
-        <v>76</v>
+        <v>73</v>
+      </c>
+      <c r="X2" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:24">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -764,69 +761,72 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R3">
         <v>1</v>
       </c>
       <c r="S3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="U3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="V3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="W3" t="s">
-        <v>76</v>
+        <v>73</v>
+      </c>
+      <c r="X3" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:24">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -835,69 +835,72 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R4">
         <v>1</v>
       </c>
       <c r="S4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="U4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="V4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="W4" t="s">
-        <v>75</v>
+        <v>72</v>
+      </c>
+      <c r="X4" t="s">
+        <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:24">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -906,69 +909,72 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R5">
         <v>1</v>
       </c>
       <c r="S5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="U5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="V5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="W5" t="s">
-        <v>75</v>
+        <v>72</v>
+      </c>
+      <c r="X5" t="s">
+        <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:24">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -977,69 +983,72 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R6">
         <v>1</v>
       </c>
       <c r="S6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="U6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="V6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="W6" t="s">
-        <v>75</v>
+        <v>72</v>
+      </c>
+      <c r="X6" t="s">
+        <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:24">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1048,69 +1057,72 @@
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R7">
         <v>1</v>
       </c>
       <c r="S7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="U7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="V7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="W7" t="s">
-        <v>75</v>
+        <v>72</v>
+      </c>
+      <c r="X7" t="s">
+        <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:24">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1119,211 +1131,220 @@
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J8" t="s">
+        <v>60</v>
+      </c>
+      <c r="K8" t="s">
+        <v>61</v>
+      </c>
+      <c r="L8" t="s">
+        <v>62</v>
+      </c>
+      <c r="M8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N8" t="s">
+        <v>64</v>
+      </c>
+      <c r="O8" t="s">
+        <v>65</v>
+      </c>
+      <c r="P8" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>67</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8" t="s">
+        <v>62</v>
+      </c>
+      <c r="T8" t="s">
+        <v>70</v>
+      </c>
+      <c r="U8" t="s">
+        <v>72</v>
+      </c>
+      <c r="V8" t="s">
+        <v>72</v>
+      </c>
+      <c r="W8" t="s">
+        <v>72</v>
+      </c>
+      <c r="X8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
         <v>57</v>
       </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="G9" t="s">
         <v>58</v>
       </c>
-      <c r="J8" t="s">
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9" t="s">
         <v>59</v>
       </c>
-      <c r="K8" t="s">
+      <c r="J9" t="s">
         <v>60</v>
       </c>
-      <c r="L8" t="s">
+      <c r="K9" t="s">
         <v>61</v>
       </c>
-      <c r="M8" t="s">
-        <v>62</v>
-      </c>
-      <c r="N8" t="s">
+      <c r="L9" t="s">
+        <v>62</v>
+      </c>
+      <c r="M9" t="s">
         <v>63</v>
       </c>
-      <c r="O8" t="s">
+      <c r="N9" t="s">
         <v>64</v>
       </c>
-      <c r="P8" t="s">
+      <c r="O9" t="s">
         <v>65</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="P9" t="s">
         <v>66</v>
       </c>
-      <c r="R8">
-        <v>1</v>
-      </c>
-      <c r="S8" t="s">
+      <c r="Q9" t="s">
+        <v>67</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9" t="s">
+        <v>62</v>
+      </c>
+      <c r="T9" t="s">
+        <v>70</v>
+      </c>
+      <c r="U9" t="s">
+        <v>72</v>
+      </c>
+      <c r="V9" t="s">
+        <v>72</v>
+      </c>
+      <c r="W9" t="s">
+        <v>72</v>
+      </c>
+      <c r="X9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" t="s">
+        <v>59</v>
+      </c>
+      <c r="J10" t="s">
+        <v>60</v>
+      </c>
+      <c r="K10" t="s">
         <v>61</v>
       </c>
-      <c r="T8" t="s">
-        <v>69</v>
-      </c>
-      <c r="U8" t="s">
-        <v>75</v>
-      </c>
-      <c r="V8" t="s">
-        <v>75</v>
-      </c>
-      <c r="W8" t="s">
-        <v>75</v>
+      <c r="L10" t="s">
+        <v>62</v>
+      </c>
+      <c r="M10" t="s">
+        <v>63</v>
+      </c>
+      <c r="N10" t="s">
+        <v>64</v>
+      </c>
+      <c r="O10" t="s">
+        <v>65</v>
+      </c>
+      <c r="P10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>67</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10" t="s">
+        <v>62</v>
+      </c>
+      <c r="T10" t="s">
+        <v>70</v>
+      </c>
+      <c r="U10" t="s">
+        <v>72</v>
+      </c>
+      <c r="V10" t="s">
+        <v>72</v>
+      </c>
+      <c r="W10" t="s">
+        <v>72</v>
+      </c>
+      <c r="X10" t="s">
+        <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
-      <c r="A9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9" t="s">
-        <v>57</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9" t="s">
-        <v>58</v>
-      </c>
-      <c r="J9" t="s">
-        <v>59</v>
-      </c>
-      <c r="K9" t="s">
-        <v>60</v>
-      </c>
-      <c r="L9" t="s">
-        <v>61</v>
-      </c>
-      <c r="M9" t="s">
-        <v>62</v>
-      </c>
-      <c r="N9" t="s">
-        <v>63</v>
-      </c>
-      <c r="O9" t="s">
-        <v>64</v>
-      </c>
-      <c r="P9" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>66</v>
-      </c>
-      <c r="R9">
-        <v>1</v>
-      </c>
-      <c r="S9" t="s">
-        <v>61</v>
-      </c>
-      <c r="T9" t="s">
-        <v>69</v>
-      </c>
-      <c r="U9" t="s">
-        <v>75</v>
-      </c>
-      <c r="V9" t="s">
-        <v>75</v>
-      </c>
-      <c r="W9" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23">
-      <c r="A10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10" t="s">
-        <v>57</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10" t="s">
-        <v>58</v>
-      </c>
-      <c r="J10" t="s">
-        <v>59</v>
-      </c>
-      <c r="K10" t="s">
-        <v>60</v>
-      </c>
-      <c r="L10" t="s">
-        <v>61</v>
-      </c>
-      <c r="M10" t="s">
-        <v>62</v>
-      </c>
-      <c r="N10" t="s">
-        <v>63</v>
-      </c>
-      <c r="O10" t="s">
-        <v>64</v>
-      </c>
-      <c r="P10" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>66</v>
-      </c>
-      <c r="R10">
-        <v>1</v>
-      </c>
-      <c r="S10" t="s">
-        <v>61</v>
-      </c>
-      <c r="T10" t="s">
-        <v>58</v>
-      </c>
-      <c r="U10" t="s">
-        <v>76</v>
-      </c>
-      <c r="V10" t="s">
-        <v>74</v>
-      </c>
-      <c r="W10" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:24">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D11">
         <v>3</v>
@@ -1332,69 +1353,72 @@
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H11">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R11">
         <v>1</v>
       </c>
       <c r="S11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T11" t="s">
         <v>70</v>
       </c>
       <c r="U11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="V11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="W11" t="s">
-        <v>76</v>
+        <v>72</v>
+      </c>
+      <c r="X11" t="s">
+        <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:24">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D12">
         <v>3</v>
@@ -1403,69 +1427,72 @@
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R12">
         <v>1</v>
       </c>
       <c r="S12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U12" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="V12" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="W12" t="s">
-        <v>76</v>
+        <v>72</v>
+      </c>
+      <c r="X12" t="s">
+        <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:24">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13">
         <v>3</v>
@@ -1474,69 +1501,72 @@
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R13">
         <v>1</v>
       </c>
       <c r="S13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="U13" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="V13" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="W13" t="s">
-        <v>75</v>
+        <v>72</v>
+      </c>
+      <c r="X13" t="s">
+        <v>72</v>
       </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:24">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1545,69 +1575,72 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H14">
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R14">
         <v>1</v>
       </c>
       <c r="S14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T14" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="U14" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="V14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="W14" t="s">
-        <v>76</v>
+        <v>72</v>
+      </c>
+      <c r="X14" t="s">
+        <v>72</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:24">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1616,69 +1649,72 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H15">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R15">
         <v>1</v>
       </c>
       <c r="S15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="U15" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="V15" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="W15" t="s">
-        <v>75</v>
+        <v>72</v>
+      </c>
+      <c r="X15" t="s">
+        <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:24">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1687,69 +1723,72 @@
         <v>3</v>
       </c>
       <c r="F16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16" t="s">
+        <v>58</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16" t="s">
+        <v>59</v>
+      </c>
+      <c r="J16" t="s">
+        <v>60</v>
+      </c>
+      <c r="K16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N16" t="s">
+        <v>64</v>
+      </c>
+      <c r="O16" t="s">
+        <v>65</v>
+      </c>
+      <c r="P16" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>67</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="S16" t="s">
+        <v>62</v>
+      </c>
+      <c r="T16" t="s">
+        <v>70</v>
+      </c>
+      <c r="U16" t="s">
+        <v>72</v>
+      </c>
+      <c r="V16" t="s">
+        <v>72</v>
+      </c>
+      <c r="W16" t="s">
+        <v>72</v>
+      </c>
+      <c r="X16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" t="s">
         <v>56</v>
-      </c>
-      <c r="G16" t="s">
-        <v>57</v>
-      </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="I16" t="s">
-        <v>58</v>
-      </c>
-      <c r="J16" t="s">
-        <v>59</v>
-      </c>
-      <c r="K16" t="s">
-        <v>60</v>
-      </c>
-      <c r="L16" t="s">
-        <v>61</v>
-      </c>
-      <c r="M16" t="s">
-        <v>62</v>
-      </c>
-      <c r="N16" t="s">
-        <v>63</v>
-      </c>
-      <c r="O16" t="s">
-        <v>64</v>
-      </c>
-      <c r="P16" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>66</v>
-      </c>
-      <c r="R16">
-        <v>1</v>
-      </c>
-      <c r="S16" t="s">
-        <v>61</v>
-      </c>
-      <c r="T16" t="s">
-        <v>72</v>
-      </c>
-      <c r="U16" t="s">
-        <v>76</v>
-      </c>
-      <c r="V16" t="s">
-        <v>76</v>
-      </c>
-      <c r="W16" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23">
-      <c r="A17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" t="s">
-        <v>55</v>
       </c>
       <c r="D17">
         <v>3</v>
@@ -1758,58 +1797,61 @@
         <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H17">
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R17">
         <v>1</v>
       </c>
       <c r="S17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T17" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="U17" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="V17" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="W17" t="s">
-        <v>76</v>
+        <v>72</v>
+      </c>
+      <c r="X17" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/Storico_Validato_Betting.xlsx
+++ b/Storico_Validato_Betting.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="82">
   <si>
     <t>Campionato</t>
   </si>
@@ -82,9 +82,30 @@
     <t>Esito_Risultato_Esatto</t>
   </si>
   <si>
+    <t>Esito_Doppia_Chance</t>
+  </si>
+  <si>
+    <t>Esito_Goal_NoGoal</t>
+  </si>
+  <si>
+    <t>Esito_U/O_1.5</t>
+  </si>
+  <si>
     <t>Esito_U/O_2.5</t>
   </si>
   <si>
+    <t>Esito_U/O_3.5</t>
+  </si>
+  <si>
+    <t>Esito_Media_Goal_Casa</t>
+  </si>
+  <si>
+    <t>Esito_Media_Goal_Trasferta</t>
+  </si>
+  <si>
+    <t>Esito_Corner_1X2</t>
+  </si>
+  <si>
     <t>Esito DC+U/O2.5</t>
   </si>
   <si>
@@ -236,6 +257,9 @@
   </si>
   <si>
     <t>PERDENTE</t>
+  </si>
+  <si>
+    <t>In attesa</t>
   </si>
 </sst>
 </file>
@@ -593,10 +617,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:AE17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -669,16 +693,37 @@
       <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -687,72 +732,93 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="J2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="L2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="M2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="N2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="O2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="P2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="Q2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="R2">
         <v>1</v>
       </c>
       <c r="S2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="T2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="U2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="V2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="W2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="X2" t="s">
-        <v>73</v>
+        <v>78</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -761,72 +827,93 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G3" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="J3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K3" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="L3" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="M3" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="N3" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="O3" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="P3" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="Q3" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="R3">
         <v>1</v>
       </c>
       <c r="S3" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="T3" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="U3" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="V3" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="W3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="X3" t="s">
-        <v>73</v>
+        <v>80</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -835,72 +922,93 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="J4" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K4" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="L4" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="M4" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="N4" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="O4" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="P4" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="Q4" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="R4">
         <v>1</v>
       </c>
       <c r="S4" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="T4" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="U4" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="V4" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="W4" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="X4" t="s">
-        <v>72</v>
+        <v>79</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -909,72 +1017,93 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G5" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="J5" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K5" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="L5" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="M5" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="N5" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="O5" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="P5" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="Q5" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="R5">
         <v>1</v>
       </c>
       <c r="S5" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="T5" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="U5" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="V5" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="W5" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="X5" t="s">
-        <v>72</v>
+        <v>79</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -983,72 +1112,93 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G6" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="J6" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K6" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="L6" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="M6" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="N6" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="O6" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="P6" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="Q6" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="R6">
         <v>1</v>
       </c>
       <c r="S6" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="T6" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="U6" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="V6" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="W6" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="X6" t="s">
-        <v>72</v>
+        <v>79</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1057,72 +1207,93 @@
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G7" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="J7" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K7" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="L7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="M7" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="N7" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="O7" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="P7" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="Q7" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="R7">
         <v>1</v>
       </c>
       <c r="S7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="T7" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="U7" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="V7" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="W7" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="X7" t="s">
-        <v>72</v>
+        <v>79</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1131,220 +1302,283 @@
         <v>0</v>
       </c>
       <c r="F8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
+        <v>66</v>
+      </c>
+      <c r="J8" t="s">
+        <v>67</v>
+      </c>
+      <c r="K8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L8" t="s">
+        <v>69</v>
+      </c>
+      <c r="M8" t="s">
+        <v>70</v>
+      </c>
+      <c r="N8" t="s">
+        <v>71</v>
+      </c>
+      <c r="O8" t="s">
+        <v>72</v>
+      </c>
+      <c r="P8" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>74</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8" t="s">
+        <v>69</v>
+      </c>
+      <c r="T8" t="s">
+        <v>77</v>
+      </c>
+      <c r="U8" t="s">
+        <v>79</v>
+      </c>
+      <c r="V8" t="s">
+        <v>79</v>
+      </c>
+      <c r="W8" t="s">
+        <v>79</v>
+      </c>
+      <c r="X8" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" t="s">
+        <v>67</v>
+      </c>
+      <c r="K9" t="s">
+        <v>68</v>
+      </c>
+      <c r="L9" t="s">
+        <v>69</v>
+      </c>
+      <c r="M9" t="s">
+        <v>70</v>
+      </c>
+      <c r="N9" t="s">
+        <v>71</v>
+      </c>
+      <c r="O9" t="s">
+        <v>72</v>
+      </c>
+      <c r="P9" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>74</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9" t="s">
+        <v>69</v>
+      </c>
+      <c r="T9" t="s">
+        <v>77</v>
+      </c>
+      <c r="U9" t="s">
+        <v>79</v>
+      </c>
+      <c r="V9" t="s">
+        <v>79</v>
+      </c>
+      <c r="W9" t="s">
+        <v>79</v>
+      </c>
+      <c r="X9" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31">
+      <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" t="s">
+        <v>66</v>
+      </c>
+      <c r="J10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K10" t="s">
+        <v>68</v>
+      </c>
+      <c r="L10" t="s">
+        <v>69</v>
+      </c>
+      <c r="M10" t="s">
+        <v>70</v>
+      </c>
+      <c r="N10" t="s">
+        <v>71</v>
+      </c>
+      <c r="O10" t="s">
+        <v>72</v>
+      </c>
+      <c r="P10" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>74</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10" t="s">
+        <v>69</v>
+      </c>
+      <c r="T10" t="s">
+        <v>77</v>
+      </c>
+      <c r="U10" t="s">
+        <v>79</v>
+      </c>
+      <c r="V10" t="s">
+        <v>79</v>
+      </c>
+      <c r="W10" t="s">
+        <v>79</v>
+      </c>
+      <c r="X10" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s">
         <v>57</v>
-      </c>
-      <c r="G8" t="s">
-        <v>58</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8" t="s">
-        <v>59</v>
-      </c>
-      <c r="J8" t="s">
-        <v>60</v>
-      </c>
-      <c r="K8" t="s">
-        <v>61</v>
-      </c>
-      <c r="L8" t="s">
-        <v>62</v>
-      </c>
-      <c r="M8" t="s">
-        <v>63</v>
-      </c>
-      <c r="N8" t="s">
-        <v>64</v>
-      </c>
-      <c r="O8" t="s">
-        <v>65</v>
-      </c>
-      <c r="P8" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>67</v>
-      </c>
-      <c r="R8">
-        <v>1</v>
-      </c>
-      <c r="S8" t="s">
-        <v>62</v>
-      </c>
-      <c r="T8" t="s">
-        <v>70</v>
-      </c>
-      <c r="U8" t="s">
-        <v>72</v>
-      </c>
-      <c r="V8" t="s">
-        <v>72</v>
-      </c>
-      <c r="W8" t="s">
-        <v>72</v>
-      </c>
-      <c r="X8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9" t="s">
-        <v>58</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9" t="s">
-        <v>59</v>
-      </c>
-      <c r="J9" t="s">
-        <v>60</v>
-      </c>
-      <c r="K9" t="s">
-        <v>61</v>
-      </c>
-      <c r="L9" t="s">
-        <v>62</v>
-      </c>
-      <c r="M9" t="s">
-        <v>63</v>
-      </c>
-      <c r="N9" t="s">
-        <v>64</v>
-      </c>
-      <c r="O9" t="s">
-        <v>65</v>
-      </c>
-      <c r="P9" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>67</v>
-      </c>
-      <c r="R9">
-        <v>1</v>
-      </c>
-      <c r="S9" t="s">
-        <v>62</v>
-      </c>
-      <c r="T9" t="s">
-        <v>70</v>
-      </c>
-      <c r="U9" t="s">
-        <v>72</v>
-      </c>
-      <c r="V9" t="s">
-        <v>72</v>
-      </c>
-      <c r="W9" t="s">
-        <v>72</v>
-      </c>
-      <c r="X9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24">
-      <c r="A10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10" t="s">
-        <v>57</v>
-      </c>
-      <c r="G10" t="s">
-        <v>58</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10" t="s">
-        <v>59</v>
-      </c>
-      <c r="J10" t="s">
-        <v>60</v>
-      </c>
-      <c r="K10" t="s">
-        <v>61</v>
-      </c>
-      <c r="L10" t="s">
-        <v>62</v>
-      </c>
-      <c r="M10" t="s">
-        <v>63</v>
-      </c>
-      <c r="N10" t="s">
-        <v>64</v>
-      </c>
-      <c r="O10" t="s">
-        <v>65</v>
-      </c>
-      <c r="P10" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>67</v>
-      </c>
-      <c r="R10">
-        <v>1</v>
-      </c>
-      <c r="S10" t="s">
-        <v>62</v>
-      </c>
-      <c r="T10" t="s">
-        <v>70</v>
-      </c>
-      <c r="U10" t="s">
-        <v>72</v>
-      </c>
-      <c r="V10" t="s">
-        <v>72</v>
-      </c>
-      <c r="W10" t="s">
-        <v>72</v>
-      </c>
-      <c r="X10" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24">
-      <c r="A11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" t="s">
-        <v>50</v>
       </c>
       <c r="D11">
         <v>3</v>
@@ -1353,72 +1587,93 @@
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G11" t="s">
+        <v>65</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11" t="s">
+        <v>66</v>
+      </c>
+      <c r="J11" t="s">
+        <v>67</v>
+      </c>
+      <c r="K11" t="s">
+        <v>68</v>
+      </c>
+      <c r="L11" t="s">
+        <v>69</v>
+      </c>
+      <c r="M11" t="s">
+        <v>70</v>
+      </c>
+      <c r="N11" t="s">
+        <v>71</v>
+      </c>
+      <c r="O11" t="s">
+        <v>72</v>
+      </c>
+      <c r="P11" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>74</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11" t="s">
+        <v>69</v>
+      </c>
+      <c r="T11" t="s">
+        <v>77</v>
+      </c>
+      <c r="U11" t="s">
+        <v>79</v>
+      </c>
+      <c r="V11" t="s">
+        <v>79</v>
+      </c>
+      <c r="W11" t="s">
+        <v>79</v>
+      </c>
+      <c r="X11" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31">
+      <c r="A12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" t="s">
         <v>58</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11" t="s">
-        <v>59</v>
-      </c>
-      <c r="J11" t="s">
-        <v>60</v>
-      </c>
-      <c r="K11" t="s">
-        <v>61</v>
-      </c>
-      <c r="L11" t="s">
-        <v>62</v>
-      </c>
-      <c r="M11" t="s">
-        <v>63</v>
-      </c>
-      <c r="N11" t="s">
-        <v>64</v>
-      </c>
-      <c r="O11" t="s">
-        <v>65</v>
-      </c>
-      <c r="P11" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>67</v>
-      </c>
-      <c r="R11">
-        <v>1</v>
-      </c>
-      <c r="S11" t="s">
-        <v>62</v>
-      </c>
-      <c r="T11" t="s">
-        <v>70</v>
-      </c>
-      <c r="U11" t="s">
-        <v>72</v>
-      </c>
-      <c r="V11" t="s">
-        <v>72</v>
-      </c>
-      <c r="W11" t="s">
-        <v>72</v>
-      </c>
-      <c r="X11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24">
-      <c r="A12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" t="s">
-        <v>51</v>
       </c>
       <c r="D12">
         <v>3</v>
@@ -1427,72 +1682,93 @@
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
       <c r="I12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J12" t="s">
+        <v>67</v>
+      </c>
+      <c r="K12" t="s">
+        <v>68</v>
+      </c>
+      <c r="L12" t="s">
+        <v>69</v>
+      </c>
+      <c r="M12" t="s">
+        <v>70</v>
+      </c>
+      <c r="N12" t="s">
+        <v>71</v>
+      </c>
+      <c r="O12" t="s">
+        <v>72</v>
+      </c>
+      <c r="P12" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>74</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12" t="s">
+        <v>69</v>
+      </c>
+      <c r="T12" t="s">
+        <v>77</v>
+      </c>
+      <c r="U12" t="s">
+        <v>79</v>
+      </c>
+      <c r="V12" t="s">
+        <v>79</v>
+      </c>
+      <c r="W12" t="s">
+        <v>79</v>
+      </c>
+      <c r="X12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31">
+      <c r="A13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" t="s">
         <v>59</v>
-      </c>
-      <c r="J12" t="s">
-        <v>60</v>
-      </c>
-      <c r="K12" t="s">
-        <v>61</v>
-      </c>
-      <c r="L12" t="s">
-        <v>62</v>
-      </c>
-      <c r="M12" t="s">
-        <v>63</v>
-      </c>
-      <c r="N12" t="s">
-        <v>64</v>
-      </c>
-      <c r="O12" t="s">
-        <v>65</v>
-      </c>
-      <c r="P12" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>67</v>
-      </c>
-      <c r="R12">
-        <v>1</v>
-      </c>
-      <c r="S12" t="s">
-        <v>62</v>
-      </c>
-      <c r="T12" t="s">
-        <v>70</v>
-      </c>
-      <c r="U12" t="s">
-        <v>72</v>
-      </c>
-      <c r="V12" t="s">
-        <v>72</v>
-      </c>
-      <c r="W12" t="s">
-        <v>72</v>
-      </c>
-      <c r="X12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" t="s">
-        <v>52</v>
       </c>
       <c r="D13">
         <v>3</v>
@@ -1501,72 +1777,93 @@
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G13" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="J13" t="s">
+        <v>67</v>
+      </c>
+      <c r="K13" t="s">
+        <v>68</v>
+      </c>
+      <c r="L13" t="s">
+        <v>69</v>
+      </c>
+      <c r="M13" t="s">
+        <v>70</v>
+      </c>
+      <c r="N13" t="s">
+        <v>71</v>
+      </c>
+      <c r="O13" t="s">
+        <v>72</v>
+      </c>
+      <c r="P13" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>74</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13" t="s">
+        <v>69</v>
+      </c>
+      <c r="T13" t="s">
+        <v>77</v>
+      </c>
+      <c r="U13" t="s">
+        <v>79</v>
+      </c>
+      <c r="V13" t="s">
+        <v>79</v>
+      </c>
+      <c r="W13" t="s">
+        <v>79</v>
+      </c>
+      <c r="X13" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31">
+      <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" t="s">
         <v>60</v>
-      </c>
-      <c r="K13" t="s">
-        <v>61</v>
-      </c>
-      <c r="L13" t="s">
-        <v>62</v>
-      </c>
-      <c r="M13" t="s">
-        <v>63</v>
-      </c>
-      <c r="N13" t="s">
-        <v>64</v>
-      </c>
-      <c r="O13" t="s">
-        <v>65</v>
-      </c>
-      <c r="P13" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>67</v>
-      </c>
-      <c r="R13">
-        <v>1</v>
-      </c>
-      <c r="S13" t="s">
-        <v>62</v>
-      </c>
-      <c r="T13" t="s">
-        <v>70</v>
-      </c>
-      <c r="U13" t="s">
-        <v>72</v>
-      </c>
-      <c r="V13" t="s">
-        <v>72</v>
-      </c>
-      <c r="W13" t="s">
-        <v>72</v>
-      </c>
-      <c r="X13" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" t="s">
-        <v>53</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1575,72 +1872,93 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G14" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H14">
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="J14" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K14" t="s">
+        <v>68</v>
+      </c>
+      <c r="L14" t="s">
+        <v>69</v>
+      </c>
+      <c r="M14" t="s">
+        <v>70</v>
+      </c>
+      <c r="N14" t="s">
+        <v>71</v>
+      </c>
+      <c r="O14" t="s">
+        <v>72</v>
+      </c>
+      <c r="P14" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>74</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14" t="s">
+        <v>69</v>
+      </c>
+      <c r="T14" t="s">
+        <v>77</v>
+      </c>
+      <c r="U14" t="s">
+        <v>79</v>
+      </c>
+      <c r="V14" t="s">
+        <v>79</v>
+      </c>
+      <c r="W14" t="s">
+        <v>79</v>
+      </c>
+      <c r="X14" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31">
+      <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" t="s">
         <v>61</v>
-      </c>
-      <c r="L14" t="s">
-        <v>62</v>
-      </c>
-      <c r="M14" t="s">
-        <v>63</v>
-      </c>
-      <c r="N14" t="s">
-        <v>64</v>
-      </c>
-      <c r="O14" t="s">
-        <v>65</v>
-      </c>
-      <c r="P14" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>67</v>
-      </c>
-      <c r="R14">
-        <v>1</v>
-      </c>
-      <c r="S14" t="s">
-        <v>62</v>
-      </c>
-      <c r="T14" t="s">
-        <v>70</v>
-      </c>
-      <c r="U14" t="s">
-        <v>72</v>
-      </c>
-      <c r="V14" t="s">
-        <v>72</v>
-      </c>
-      <c r="W14" t="s">
-        <v>72</v>
-      </c>
-      <c r="X14" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24">
-      <c r="A15" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" t="s">
-        <v>54</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1649,72 +1967,93 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G15" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H15">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="J15" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K15" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="L15" t="s">
+        <v>69</v>
+      </c>
+      <c r="M15" t="s">
+        <v>70</v>
+      </c>
+      <c r="N15" t="s">
+        <v>71</v>
+      </c>
+      <c r="O15" t="s">
+        <v>72</v>
+      </c>
+      <c r="P15" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>74</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15" t="s">
+        <v>69</v>
+      </c>
+      <c r="T15" t="s">
+        <v>77</v>
+      </c>
+      <c r="U15" t="s">
+        <v>79</v>
+      </c>
+      <c r="V15" t="s">
+        <v>79</v>
+      </c>
+      <c r="W15" t="s">
+        <v>79</v>
+      </c>
+      <c r="X15" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" t="s">
         <v>62</v>
-      </c>
-      <c r="M15" t="s">
-        <v>63</v>
-      </c>
-      <c r="N15" t="s">
-        <v>64</v>
-      </c>
-      <c r="O15" t="s">
-        <v>65</v>
-      </c>
-      <c r="P15" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>67</v>
-      </c>
-      <c r="R15">
-        <v>1</v>
-      </c>
-      <c r="S15" t="s">
-        <v>62</v>
-      </c>
-      <c r="T15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V15" t="s">
-        <v>72</v>
-      </c>
-      <c r="W15" t="s">
-        <v>72</v>
-      </c>
-      <c r="X15" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24">
-      <c r="A16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" t="s">
-        <v>55</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1723,72 +2062,93 @@
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G16" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H16">
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="J16" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K16" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="L16" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="M16" t="s">
+        <v>70</v>
+      </c>
+      <c r="N16" t="s">
+        <v>71</v>
+      </c>
+      <c r="O16" t="s">
+        <v>72</v>
+      </c>
+      <c r="P16" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>74</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="S16" t="s">
+        <v>69</v>
+      </c>
+      <c r="T16" t="s">
+        <v>77</v>
+      </c>
+      <c r="U16" t="s">
+        <v>79</v>
+      </c>
+      <c r="V16" t="s">
+        <v>79</v>
+      </c>
+      <c r="W16" t="s">
+        <v>79</v>
+      </c>
+      <c r="X16" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31">
+      <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" t="s">
         <v>63</v>
-      </c>
-      <c r="N16" t="s">
-        <v>64</v>
-      </c>
-      <c r="O16" t="s">
-        <v>65</v>
-      </c>
-      <c r="P16" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>67</v>
-      </c>
-      <c r="R16">
-        <v>1</v>
-      </c>
-      <c r="S16" t="s">
-        <v>62</v>
-      </c>
-      <c r="T16" t="s">
-        <v>70</v>
-      </c>
-      <c r="U16" t="s">
-        <v>72</v>
-      </c>
-      <c r="V16" t="s">
-        <v>72</v>
-      </c>
-      <c r="W16" t="s">
-        <v>72</v>
-      </c>
-      <c r="X16" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24">
-      <c r="A17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" t="s">
-        <v>56</v>
       </c>
       <c r="D17">
         <v>3</v>
@@ -1797,61 +2157,82 @@
         <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G17" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H17">
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="J17" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="L17" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="M17" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="N17" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="O17" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="P17" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="Q17" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="R17">
         <v>1</v>
       </c>
       <c r="S17" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="T17" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="U17" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="V17" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="W17" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="X17" t="s">
-        <v>72</v>
+        <v>79</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/Storico_Validato_Betting.xlsx
+++ b/Storico_Validato_Betting.xlsx
@@ -103,10 +103,10 @@
     <t>Esito_Media_Goal_Trasferta</t>
   </si>
   <si>
+    <t>Esito_DC+U/O2.5</t>
+  </si>
+  <si>
     <t>Esito_Corner_1X2</t>
-  </si>
-  <si>
-    <t>Esito DC+U/O2.5</t>
   </si>
   <si>
     <t>FIFA World Cup</t>
@@ -804,10 +804,10 @@
         <v>80</v>
       </c>
       <c r="AD2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE2" t="s">
         <v>81</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:31">
@@ -899,10 +899,10 @@
         <v>80</v>
       </c>
       <c r="AD3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE3" t="s">
         <v>81</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:31">

--- a/Storico_Validato_Betting.xlsx
+++ b/Storico_Validato_Betting.xlsx
@@ -103,10 +103,10 @@
     <t>Esito_Media_Goal_Trasferta</t>
   </si>
   <si>
+    <t>Esito_Corner_1X2</t>
+  </si>
+  <si>
     <t>Esito_DC+U/O2.5</t>
-  </si>
-  <si>
-    <t>Esito_Corner_1X2</t>
   </si>
   <si>
     <t>FIFA World Cup</t>
@@ -804,10 +804,10 @@
         <v>80</v>
       </c>
       <c r="AD2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE2" t="s">
         <v>80</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:31">
@@ -899,10 +899,10 @@
         <v>80</v>
       </c>
       <c r="AD3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE3" t="s">
         <v>80</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:31">

--- a/Storico_Validato_Betting.xlsx
+++ b/Storico_Validato_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE15"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,70 +516,60 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>PRONOSTICO</t>
+          <t>Risultato_Reale</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>U/O 2.5</t>
+          <t>Esito_1X2</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Risultato_Reale</t>
+          <t>Esito_Risultato_Esatto</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Esito_1X2</t>
+          <t>Esito_Doppia_Chance</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Esito_Risultato_Esatto</t>
+          <t>Esito_Goal_NoGoal</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Esito_Doppia_Chance</t>
+          <t>Esito_U/O_1.5</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Esito_Goal_NoGoal</t>
+          <t>Esito_U/O_2.5</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Esito_U/O_1.5</t>
+          <t>Esito_U/O_3.5</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Esito_U/O_2.5</t>
+          <t>Esito_Media_Goal_Casa</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Esito_U/O_3.5</t>
+          <t>Esito_Media_Goal_Trasferta</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Esito_Media_Goal_Casa</t>
+          <t>Esito_Corner_1X2</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Esito_Media_Goal_Trasferta</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Esito_Corner_1X2</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Esito_DC+U/O2.5</t>
         </is>
@@ -593,12 +583,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17/06/2026 19:00</t>
+          <t>17/06/2026 22:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal - Congo DR</t>
+          <t>England - Croatia</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -609,12 +599,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -665,17 +655,19 @@
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R2" t="n">
-        <v>1</v>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
+        </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>UNDER 2.5</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -719,16 +711,6 @@
         </is>
       </c>
       <c r="AC2" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -742,12 +724,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17/06/2026 22:00</t>
+          <t>18/06/2026 01:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>England - Croatia</t>
+          <t>Ghana - Panama</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -758,12 +740,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -814,17 +796,19 @@
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R3" t="n">
-        <v>1</v>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
+        </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>UNDER 2.5</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -868,16 +852,6 @@
         </is>
       </c>
       <c r="AC3" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -891,12 +865,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18/06/2026 01:00</t>
+          <t>18/06/2026 04:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ghana - Panama</t>
+          <t>Uzbekistan - Colombia</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -907,12 +881,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -963,17 +937,19 @@
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R4" t="n">
-        <v>1</v>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
+        </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>UNDER 2.5</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -1017,16 +993,6 @@
         </is>
       </c>
       <c r="AC4" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -1040,12 +1006,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18/06/2026 04:00</t>
+          <t>18/06/2026 18:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan - Colombia</t>
+          <t>Czechia - South Africa</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1056,12 +1022,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1112,17 +1078,19 @@
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R5" t="n">
-        <v>1</v>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
+        </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>UNDER 2.5</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1166,16 +1134,6 @@
         </is>
       </c>
       <c r="AC5" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -1189,28 +1147,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18/06/2026 18:00</t>
+          <t>18/06/2026 21:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czechia - South Africa</t>
+          <t>Switzerland - Bosnia-Herzegovina</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1261,17 +1219,19 @@
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R6" t="n">
-        <v>1</v>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
+        </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>UNDER 2.5</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1315,16 +1275,6 @@
         </is>
       </c>
       <c r="AC6" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -1338,12 +1288,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18/06/2026 21:00</t>
+          <t>19/06/2026 00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Switzerland - Bosnia-Herzegovina</t>
+          <t>Canada - Qatar</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1354,12 +1304,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1410,17 +1360,19 @@
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R7" t="n">
-        <v>1</v>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
+        </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>UNDER 2.5</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1464,16 +1416,6 @@
         </is>
       </c>
       <c r="AC7" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -1487,28 +1429,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19/06/2026 00:00</t>
+          <t>19/06/2026 03:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Canada - Qatar</t>
+          <t>Mexico - South Korea</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1559,17 +1501,19 @@
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R8" t="n">
-        <v>1</v>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
+        </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>UNDER 2.5</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1613,16 +1557,6 @@
         </is>
       </c>
       <c r="AC8" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -1636,12 +1570,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19/06/2026 03:00</t>
+          <t>19/06/2026 21:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mexico - South Korea</t>
+          <t>United States - Australia</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1652,12 +1586,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1708,17 +1642,19 @@
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R9" t="n">
-        <v>1</v>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
+        </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>UNDER 2.5</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1762,16 +1698,6 @@
         </is>
       </c>
       <c r="AC9" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -1785,28 +1711,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19/06/2026 21:00</t>
+          <t>20/06/2026 00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>United States - Australia</t>
+          <t>Scotland - Morocco</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1857,17 +1783,19 @@
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R10" t="n">
-        <v>1</v>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
+        </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>UNDER 2.5</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1911,16 +1839,6 @@
         </is>
       </c>
       <c r="AC10" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -1934,28 +1852,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20/06/2026 00:00</t>
+          <t>20/06/2026 02:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Scotland - Morocco</t>
+          <t>Brazil - Haiti</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2006,17 +1924,19 @@
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R11" t="n">
-        <v>1</v>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
+        </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>UNDER 2.5</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -2060,16 +1980,6 @@
         </is>
       </c>
       <c r="AC11" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -2083,28 +1993,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20/06/2026 02:30</t>
+          <t>20/06/2026 05:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil - Haiti</t>
+          <t>Turkey - Paraguay</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2155,17 +2065,19 @@
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R12" t="n">
-        <v>1</v>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
+        </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>UNDER 2.5</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2209,16 +2121,6 @@
         </is>
       </c>
       <c r="AC12" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -2232,28 +2134,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20/06/2026 05:00</t>
+          <t>20/06/2026 19:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey - Paraguay</t>
+          <t>Netherlands - Sweden</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2304,17 +2206,19 @@
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R13" t="n">
-        <v>1</v>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
+        </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>UNDER 2.5</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2358,16 +2262,6 @@
         </is>
       </c>
       <c r="AC13" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -2381,28 +2275,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20/06/2026 19:00</t>
+          <t>20/06/2026 22:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Netherlands - Sweden</t>
+          <t>Germany - Ivory Coast</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
         <v>3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2453,17 +2347,19 @@
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R14" t="n">
-        <v>1</v>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
+        </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>UNDER 2.5</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2507,16 +2403,6 @@
         </is>
       </c>
       <c r="AC14" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -2530,28 +2416,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20/06/2026 22:00</t>
+          <t>21/06/2026 02:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Germany - Ivory Coast</t>
+          <t>Ecuador - Curaçao</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -2602,70 +2488,626 @@
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R15" t="n">
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>21/06/2026 06:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Tunisia - Japan</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
         <v>1</v>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>NOGOAL</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1X+UNDER</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>21/06/2026 18:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Spain - Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>NOGOAL</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1X+UNDER</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>21/06/2026 21:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Belgium - Iran</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>NOGOAL</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1X+UNDER</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>22/06/2026 00:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Uruguay - Cape Verde Islands</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>NOGOAL</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1X+UNDER</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>

--- a/Storico_Validato_Betting.xlsx
+++ b/Storico_Validato_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,12 +583,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17/06/2026 22:00</t>
+          <t>18/06/2026 01:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>England - Croatia</t>
+          <t>Ghana - Panama</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -724,12 +724,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18/06/2026 01:00</t>
+          <t>18/06/2026 04:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ghana - Panama</t>
+          <t>Uzbekistan - Colombia</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -865,12 +865,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18/06/2026 04:00</t>
+          <t>18/06/2026 18:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan - Colombia</t>
+          <t>Czechia - South Africa</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1006,19 +1006,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18/06/2026 18:00</t>
+          <t>18/06/2026 21:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czechia - South Africa</t>
+          <t>Switzerland - Bosnia-Herzegovina</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18/06/2026 21:00</t>
+          <t>19/06/2026 00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Switzerland - Bosnia-Herzegovina</t>
+          <t>Canada - Qatar</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1288,19 +1288,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19/06/2026 00:00</t>
+          <t>19/06/2026 03:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Canada - Qatar</t>
+          <t>Mexico - South Korea</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1429,12 +1429,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19/06/2026 03:00</t>
+          <t>19/06/2026 21:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mexico - South Korea</t>
+          <t>United States - Australia</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1570,19 +1570,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19/06/2026 21:00</t>
+          <t>20/06/2026 00:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>United States - Australia</t>
+          <t>Scotland - Morocco</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1711,19 +1711,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20/06/2026 00:00</t>
+          <t>20/06/2026 02:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Scotland - Morocco</t>
+          <t>Brazil - Haiti</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1852,16 +1852,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20/06/2026 02:30</t>
+          <t>20/06/2026 05:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil - Haiti</t>
+          <t>Turkey - Paraguay</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1993,19 +1993,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20/06/2026 05:00</t>
+          <t>20/06/2026 19:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey - Paraguay</t>
+          <t>Netherlands - Sweden</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,16 +2134,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20/06/2026 19:00</t>
+          <t>20/06/2026 22:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Netherlands - Sweden</t>
+          <t>Germany - Ivory Coast</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
         <v>3</v>
@@ -2275,19 +2275,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20/06/2026 22:00</t>
+          <t>21/06/2026 02:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Germany - Ivory Coast</t>
+          <t>Ecuador - Curaçao</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2416,19 +2416,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21/06/2026 02:00</t>
+          <t>21/06/2026 06:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ecuador - Curaçao</t>
+          <t>Tunisia - Japan</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2557,16 +2557,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21/06/2026 06:00</t>
+          <t>21/06/2026 18:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia - Japan</t>
+          <t>Spain - Saudi Arabia</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -2698,12 +2698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21/06/2026 18:00</t>
+          <t>21/06/2026 21:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain - Saudi Arabia</t>
+          <t>Belgium - Iran</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21/06/2026 21:00</t>
+          <t>22/06/2026 00:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Belgium - Iran</t>
+          <t>Uruguay - Cape Verde Islands</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2967,147 +2967,6 @@
         </is>
       </c>
       <c r="AC18" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>FIFA World Cup</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>22/06/2026 00:00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Uruguay - Cape Verde Islands</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>1X</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>OVER 1.5</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>UNDER 3.5</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>NOGOAL</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>1X+UNDER</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>

--- a/Storico_Validato_Betting.xlsx
+++ b/Storico_Validato_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,12 +583,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18/06/2026 01:00</t>
+          <t>17/06/2026 22:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ghana - Panama</t>
+          <t>England - Croatia</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -657,62 +657,62 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>In attesa</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
     </row>
@@ -724,12 +724,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18/06/2026 04:00</t>
+          <t>18/06/2026 01:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan - Colombia</t>
+          <t>Ghana - Panama</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -865,12 +865,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18/06/2026 18:00</t>
+          <t>18/06/2026 04:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czechia - South Africa</t>
+          <t>Uzbekistan - Colombia</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1006,19 +1006,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18/06/2026 21:00</t>
+          <t>18/06/2026 18:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Switzerland - Bosnia-Herzegovina</t>
+          <t>Czechia - South Africa</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19/06/2026 00:00</t>
+          <t>18/06/2026 21:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Canada - Qatar</t>
+          <t>Switzerland - Bosnia-Herzegovina</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1288,19 +1288,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19/06/2026 03:00</t>
+          <t>19/06/2026 00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mexico - South Korea</t>
+          <t>Canada - Qatar</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1429,12 +1429,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19/06/2026 21:00</t>
+          <t>19/06/2026 03:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>United States - Australia</t>
+          <t>Mexico - South Korea</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1570,19 +1570,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20/06/2026 00:00</t>
+          <t>19/06/2026 21:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Scotland - Morocco</t>
+          <t>United States - Australia</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1711,19 +1711,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20/06/2026 02:30</t>
+          <t>20/06/2026 00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil - Haiti</t>
+          <t>Scotland - Morocco</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
         <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1852,16 +1852,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20/06/2026 05:00</t>
+          <t>20/06/2026 02:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey - Paraguay</t>
+          <t>Brazil - Haiti</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1993,19 +1993,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20/06/2026 19:00</t>
+          <t>20/06/2026 05:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Netherlands - Sweden</t>
+          <t>Turkey - Paraguay</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,16 +2134,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20/06/2026 22:00</t>
+          <t>20/06/2026 19:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Germany - Ivory Coast</t>
+          <t>Netherlands - Sweden</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>3</v>
@@ -2275,19 +2275,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21/06/2026 02:00</t>
+          <t>20/06/2026 22:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ecuador - Curaçao</t>
+          <t>Germany - Ivory Coast</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2416,19 +2416,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21/06/2026 06:00</t>
+          <t>21/06/2026 02:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia - Japan</t>
+          <t>Ecuador - Curaçao</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2557,16 +2557,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21/06/2026 18:00</t>
+          <t>21/06/2026 06:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain - Saudi Arabia</t>
+          <t>Tunisia - Japan</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -2698,12 +2698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21/06/2026 21:00</t>
+          <t>21/06/2026 18:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Belgium - Iran</t>
+          <t>Spain - Saudi Arabia</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>22/06/2026 00:00</t>
+          <t>21/06/2026 21:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uruguay - Cape Verde Islands</t>
+          <t>Belgium - Iran</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2967,6 +2967,147 @@
         </is>
       </c>
       <c r="AC18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>22/06/2026 00:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Uruguay - Cape Verde Islands</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>NOGOAL</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1X+UNDER</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>

--- a/Storico_Validato_Betting.xlsx
+++ b/Storico_Validato_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,12 +583,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17/06/2026 22:00</t>
+          <t>18/06/2026 18:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>England - Croatia</t>
+          <t>Czechia - South Africa</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -657,62 +657,62 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>In attesa</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
     </row>
@@ -724,19 +724,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18/06/2026 01:00</t>
+          <t>18/06/2026 21:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ghana - Panama</t>
+          <t>Switzerland - Bosnia-Herzegovina</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,19 +865,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18/06/2026 04:00</t>
+          <t>19/06/2026 00:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan - Colombia</t>
+          <t>Canada - Qatar</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1006,19 +1006,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18/06/2026 18:00</t>
+          <t>19/06/2026 03:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czechia - South Africa</t>
+          <t>Mexico - South Korea</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1147,19 +1147,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18/06/2026 21:00</t>
+          <t>19/06/2026 21:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Switzerland - Bosnia-Herzegovina</t>
+          <t>United States - Australia</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,16 +1288,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19/06/2026 00:00</t>
+          <t>20/06/2026 00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Canada - Qatar</t>
+          <t>Scotland - Morocco</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -1429,19 +1429,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19/06/2026 03:00</t>
+          <t>20/06/2026 02:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mexico - South Korea</t>
+          <t>Brazil - Haiti</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1570,19 +1570,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19/06/2026 21:00</t>
+          <t>20/06/2026 05:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>United States - Australia</t>
+          <t>Turkey - Paraguay</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1711,19 +1711,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20/06/2026 00:00</t>
+          <t>20/06/2026 19:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Scotland - Morocco</t>
+          <t>Netherlands - Sweden</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
         <v>3</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1852,19 +1852,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20/06/2026 02:30</t>
+          <t>20/06/2026 22:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil - Haiti</t>
+          <t>Germany - Ivory Coast</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1993,12 +1993,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20/06/2026 05:00</t>
+          <t>21/06/2026 02:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey - Paraguay</t>
+          <t>Ecuador - Curaçao</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -2134,19 +2134,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20/06/2026 19:00</t>
+          <t>21/06/2026 06:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Netherlands - Sweden</t>
+          <t>Tunisia - Japan</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2275,19 +2275,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20/06/2026 22:00</t>
+          <t>21/06/2026 18:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Germany - Ivory Coast</t>
+          <t>Spain - Saudi Arabia</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2416,19 +2416,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21/06/2026 02:00</t>
+          <t>21/06/2026 21:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ecuador - Curaçao</t>
+          <t>Belgium - Iran</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2557,16 +2557,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21/06/2026 06:00</t>
+          <t>22/06/2026 00:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia - Japan</t>
+          <t>Uruguay - Cape Verde Islands</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -2685,429 +2685,6 @@
         </is>
       </c>
       <c r="AC16" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>FIFA World Cup</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>21/06/2026 18:00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Spain - Saudi Arabia</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>1X</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>OVER 1.5</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>UNDER 3.5</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>NOGOAL</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>1X+UNDER</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>FIFA World Cup</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>21/06/2026 21:00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Belgium - Iran</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>1X</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>OVER 1.5</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>UNDER 3.5</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>NOGOAL</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>1X+UNDER</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>FIFA World Cup</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>22/06/2026 00:00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Uruguay - Cape Verde Islands</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>1X</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>OVER 1.5</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>UNDER 3.5</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>NOGOAL</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>1X+UNDER</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>

--- a/Storico_Validato_Betting.xlsx
+++ b/Storico_Validato_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2685,6 +2685,429 @@
         </is>
       </c>
       <c r="AC16" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>22/06/2026 03:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>New Zealand - Egypt</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>NOGOAL</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1X+UNDER</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>22/06/2026 19:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Argentina - Austria</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>NOGOAL</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1X+UNDER</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>22/06/2026 23:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>France - Iraq</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>NOGOAL</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1X+UNDER</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>

--- a/Storico_Validato_Betting.xlsx
+++ b/Storico_Validato_Betting.xlsx
@@ -657,62 +657,62 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>In attesa</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
     </row>
@@ -798,62 +798,62 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>In attesa</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
     </row>
@@ -939,62 +939,62 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
+          <t>6-0</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>In attesa</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
     </row>
@@ -1080,62 +1080,62 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>In attesa</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
     </row>

--- a/Storico_Validato_Betting.xlsx
+++ b/Storico_Validato_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AE20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,60 +516,70 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>Pronostico_MG_Casa</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Pronostico_MG_Trasferta</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>Risultato_Reale</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Esito_1X2</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Esito_Risultato_Esatto</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Esito_Doppia_Chance</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Esito_Goal_NoGoal</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Esito_U/O_1.5</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Esito_U/O_2.5</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Esito_U/O_3.5</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Esito_Media_Goal_Casa</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Esito_Media_Goal_Trasferta</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Esito_Corner_1X2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Esito_DC+U/O2.5</t>
         </is>
@@ -583,29 +593,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18/06/2026 18:00</t>
+          <t>19/06/2026 21:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Czechia - South Africa</t>
+          <t>United States - Australia</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.1</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -657,62 +663,72 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>In attesa</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
         </is>
       </c>
     </row>
@@ -724,29 +740,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18/06/2026 21:00</t>
+          <t>20/06/2026 00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Switzerland - Bosnia-Herzegovina</t>
+          <t>Scotland - Morocco</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+      <c r="F3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.1</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -798,62 +810,72 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>In attesa</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
         </is>
       </c>
     </row>
@@ -865,29 +887,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>19/06/2026 00:00</t>
+          <t>20/06/2026 02:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Canada - Qatar</t>
+          <t>Brazil - Haiti</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.1</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -939,62 +957,72 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>6-0</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>In attesa</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
         </is>
       </c>
     </row>
@@ -1006,29 +1034,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19/06/2026 03:00</t>
+          <t>20/06/2026 05:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mexico - South Korea</t>
+          <t>Turkey - Paraguay</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.1</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
@@ -1080,62 +1104,72 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>In attesa</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
         </is>
       </c>
     </row>
@@ -1147,29 +1181,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19/06/2026 21:00</t>
+          <t>20/06/2026 19:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>United States - Australia</t>
+          <t>Netherlands - Sweden</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+      <c r="F6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.1</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
@@ -1221,19 +1251,19 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -1275,6 +1305,16 @@
         </is>
       </c>
       <c r="AC6" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -1288,29 +1328,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20/06/2026 00:00</t>
+          <t>20/06/2026 22:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Scotland - Morocco</t>
+          <t>Germany - Ivory Coast</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.1</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -1362,19 +1398,19 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -1416,6 +1452,16 @@
         </is>
       </c>
       <c r="AC7" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -1429,29 +1475,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20/06/2026 02:30</t>
+          <t>21/06/2026 02:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil - Haiti</t>
+          <t>Ecuador - Curaçao</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+      <c r="F8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.1</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -1503,19 +1545,19 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -1557,6 +1599,16 @@
         </is>
       </c>
       <c r="AC8" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -1570,29 +1622,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20/06/2026 05:00</t>
+          <t>21/06/2026 06:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey - Paraguay</t>
+          <t>Tunisia - Japan</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.1</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
@@ -1644,19 +1692,19 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -1698,6 +1746,16 @@
         </is>
       </c>
       <c r="AC9" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -1711,29 +1769,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20/06/2026 19:00</t>
+          <t>21/06/2026 18:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Netherlands - Sweden</t>
+          <t>Spain - Saudi Arabia</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.1</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -1785,19 +1839,19 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -1839,6 +1893,16 @@
         </is>
       </c>
       <c r="AC10" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -1852,29 +1916,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20/06/2026 22:00</t>
+          <t>21/06/2026 21:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Germany - Ivory Coast</t>
+          <t>Belgium - Iran</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.1</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
@@ -1926,19 +1986,19 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -1980,6 +2040,16 @@
         </is>
       </c>
       <c r="AC11" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -1993,29 +2063,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21/06/2026 02:00</t>
+          <t>22/06/2026 00:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ecuador - Curaçao</t>
+          <t>Uruguay - Cape Verde Islands</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.1</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -2067,19 +2133,19 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -2121,6 +2187,16 @@
         </is>
       </c>
       <c r="AC12" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -2134,29 +2210,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21/06/2026 06:00</t>
+          <t>22/06/2026 03:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia - Japan</t>
+          <t>New Zealand - Egypt</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+      <c r="F13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.1</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
@@ -2208,19 +2280,19 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -2262,6 +2334,16 @@
         </is>
       </c>
       <c r="AC13" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -2275,29 +2357,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21/06/2026 18:00</t>
+          <t>22/06/2026 19:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain - Saudi Arabia</t>
+          <t>Argentina - Austria</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.1</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
@@ -2349,19 +2427,19 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -2403,6 +2481,16 @@
         </is>
       </c>
       <c r="AC14" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -2416,29 +2504,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21/06/2026 21:00</t>
+          <t>22/06/2026 23:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Belgium - Iran</t>
+          <t>France - Iraq</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.1</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -2490,19 +2574,19 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -2544,6 +2628,16 @@
         </is>
       </c>
       <c r="AC15" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -2557,29 +2651,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>22/06/2026 00:00</t>
+          <t>23/06/2026 02:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uruguay - Cape Verde Islands</t>
+          <t>Norway - Senegal</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.1</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
@@ -2631,19 +2721,19 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -2685,6 +2775,16 @@
         </is>
       </c>
       <c r="AC16" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -2698,29 +2798,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>22/06/2026 03:00</t>
+          <t>23/06/2026 05:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New Zealand - Egypt</t>
+          <t>Jordan - Algeria</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.1</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
@@ -2772,19 +2868,19 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -2826,6 +2922,16 @@
         </is>
       </c>
       <c r="AC17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -2839,29 +2945,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>22/06/2026 19:00</t>
+          <t>23/06/2026 19:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina - Austria</t>
+          <t>Portugal - Uzbekistan</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.1</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
@@ -2913,19 +3015,19 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -2967,6 +3069,16 @@
         </is>
       </c>
       <c r="AC18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -2980,29 +3092,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>22/06/2026 23:00</t>
+          <t>23/06/2026 22:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France - Iraq</t>
+          <t>England - Ghana</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.1</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
@@ -3054,19 +3162,19 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -3108,6 +3216,163 @@
         </is>
       </c>
       <c r="AC19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>24/06/2026 01:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Panama - Croatia</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>NOGOAL</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1X+UNDER</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>

--- a/Storico_Validato_Betting.xlsx
+++ b/Storico_Validato_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE20"/>
+  <dimension ref="A1:AI20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,125 +461,145 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Media_Goal_Subiti_Casa</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Media_Goal_Trasferta</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Media_Goal_Subiti_Trasferta</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Forma_Casa</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Forma_Trasferta</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Risultato_Esatto</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Doppia_Chance</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>U/O_1.5</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>U/O_2.5</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>U/O_3.5</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Goal_NoGoal</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>DC+U/O2.5</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Corner_1X2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Odds_1X2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Pronostico_MG_Casa</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Pronostico_MG_Trasferta</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Risultato_Reale</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Esito_1X2</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Esito_Risultato_Esatto</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Esito_Doppia_Chance</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Esito_Goal_NoGoal</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Esito_U/O_1.5</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Esito_U/O_2.5</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Esito_U/O_3.5</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Esito_Media_Goal_Casa</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Esito_Media_Goal_Trasferta</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Esito_Corner_1X2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Esito_DC+U/O2.5</t>
         </is>
@@ -611,91 +631,79 @@
         <v>1.2</v>
       </c>
       <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
         <v>1.1</v>
       </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -727,6 +735,26 @@
         </is>
       </c>
       <c r="AE2" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -758,91 +786,79 @@
         <v>1.2</v>
       </c>
       <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
         <v>1.1</v>
       </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -874,6 +890,26 @@
         </is>
       </c>
       <c r="AE3" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -905,91 +941,79 @@
         <v>1.2</v>
       </c>
       <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
         <v>1.1</v>
       </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -1021,6 +1045,26 @@
         </is>
       </c>
       <c r="AE4" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -1052,91 +1096,79 @@
         <v>1.2</v>
       </c>
       <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
         <v>1.1</v>
       </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -1168,6 +1200,26 @@
         </is>
       </c>
       <c r="AE5" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -1199,91 +1251,79 @@
         <v>1.2</v>
       </c>
       <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
         <v>1.1</v>
       </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -1315,6 +1355,26 @@
         </is>
       </c>
       <c r="AE6" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -1346,91 +1406,79 @@
         <v>1.2</v>
       </c>
       <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
         <v>1.1</v>
       </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -1462,6 +1510,26 @@
         </is>
       </c>
       <c r="AE7" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -1493,91 +1561,79 @@
         <v>1.2</v>
       </c>
       <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
         <v>1.1</v>
       </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -1609,6 +1665,26 @@
         </is>
       </c>
       <c r="AE8" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -1640,91 +1716,79 @@
         <v>1.2</v>
       </c>
       <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
         <v>1.1</v>
       </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="Y9" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -1756,6 +1820,26 @@
         </is>
       </c>
       <c r="AE9" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -1787,91 +1871,79 @@
         <v>1.2</v>
       </c>
       <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
         <v>1.1</v>
       </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="Y10" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -1903,6 +1975,26 @@
         </is>
       </c>
       <c r="AE10" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -1934,91 +2026,79 @@
         <v>1.2</v>
       </c>
       <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
         <v>1.1</v>
       </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
         <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="Y11" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -2050,6 +2130,26 @@
         </is>
       </c>
       <c r="AE11" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -2081,91 +2181,79 @@
         <v>1.2</v>
       </c>
       <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
         <v>1.1</v>
       </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
         <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="Y12" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -2197,6 +2285,26 @@
         </is>
       </c>
       <c r="AE12" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -2228,91 +2336,79 @@
         <v>1.2</v>
       </c>
       <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
         <v>1.1</v>
       </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
         <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="Y13" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -2344,6 +2440,26 @@
         </is>
       </c>
       <c r="AE13" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -2375,91 +2491,79 @@
         <v>1.2</v>
       </c>
       <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
         <v>1.1</v>
       </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="Y14" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -2491,6 +2595,26 @@
         </is>
       </c>
       <c r="AE14" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -2522,91 +2646,79 @@
         <v>1.2</v>
       </c>
       <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
         <v>1.1</v>
       </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
         <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="Y15" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -2638,6 +2750,26 @@
         </is>
       </c>
       <c r="AE15" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -2669,91 +2801,79 @@
         <v>1.2</v>
       </c>
       <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
         <v>1.1</v>
       </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="Y16" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -2785,6 +2905,26 @@
         </is>
       </c>
       <c r="AE16" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -2816,91 +2956,79 @@
         <v>1.2</v>
       </c>
       <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
         <v>1.1</v>
       </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
         <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="Y17" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -2932,6 +3060,26 @@
         </is>
       </c>
       <c r="AE17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -2963,91 +3111,79 @@
         <v>1.2</v>
       </c>
       <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
         <v>1.1</v>
       </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
         <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="Y18" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -3079,6 +3215,26 @@
         </is>
       </c>
       <c r="AE18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -3110,91 +3266,79 @@
         <v>1.2</v>
       </c>
       <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
         <v>1.1</v>
       </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
         <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="Y19" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -3226,6 +3370,26 @@
         </is>
       </c>
       <c r="AE19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
@@ -3257,91 +3421,79 @@
         <v>1.2</v>
       </c>
       <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
         <v>1.1</v>
       </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
         <is>
           <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
       <c r="Y20" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
@@ -3373,6 +3525,26 @@
         </is>
       </c>
       <c r="AE20" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>

--- a/Storico_Validato_Betting.xlsx
+++ b/Storico_Validato_Betting.xlsx
@@ -701,62 +701,62 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>In attesa</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>In attesa</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
     </row>
@@ -1011,62 +1011,62 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>In attesa</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
     </row>
@@ -1166,62 +1166,62 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>VINCENTE</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>In attesa</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Non Disponibile</t>
+          <t>PERDENTE</t>
         </is>
       </c>
     </row>

--- a/Storico_Validato_Betting.xlsx
+++ b/Storico_Validato_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI20"/>
+  <dimension ref="A1:AI21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,16 +613,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19/06/2026 21:00</t>
+          <t>20/06/2026 19:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>United States - Australia</t>
+          <t>Netherlands - Sweden</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
@@ -701,62 +701,62 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>In attesa</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
     </row>
@@ -768,19 +768,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20/06/2026 00:00</t>
+          <t>20/06/2026 22:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Scotland - Morocco</t>
+          <t>Germany - Ivory Coast</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>1.2</v>
@@ -856,62 +856,62 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>In attesa</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
     </row>
@@ -923,16 +923,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20/06/2026 02:30</t>
+          <t>21/06/2026 02:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brazil - Haiti</t>
+          <t>Ecuador - Curaçao</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1011,62 +1011,62 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>In attesa</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
     </row>
@@ -1078,19 +1078,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20/06/2026 05:00</t>
+          <t>21/06/2026 06:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey - Paraguay</t>
+          <t>Tunisia - Japan</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>1.2</v>
@@ -1166,62 +1166,62 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>VINCENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>In attesa</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>PERDENTE</t>
+          <t>Non Disponibile</t>
         </is>
       </c>
     </row>
@@ -1233,19 +1233,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20/06/2026 19:00</t>
+          <t>21/06/2026 18:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Netherlands - Sweden</t>
+          <t>Spain - Saudi Arabia</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>1.2</v>
@@ -1388,19 +1388,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20/06/2026 22:00</t>
+          <t>21/06/2026 21:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Germany - Ivory Coast</t>
+          <t>Belgium - Iran</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>1.2</v>
@@ -1543,19 +1543,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21/06/2026 02:00</t>
+          <t>22/06/2026 00:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ecuador - Curaçao</t>
+          <t>Uruguay - Cape Verde Islands</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>1.2</v>
@@ -1698,16 +1698,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21/06/2026 06:00</t>
+          <t>22/06/2026 03:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia - Japan</t>
+          <t>New Zealand - Egypt</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -1853,19 +1853,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21/06/2026 18:00</t>
+          <t>22/06/2026 19:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain - Saudi Arabia</t>
+          <t>Argentina - Austria</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>1.2</v>
@@ -2008,19 +2008,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21/06/2026 21:00</t>
+          <t>22/06/2026 23:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Belgium - Iran</t>
+          <t>France - Iraq</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>1.2</v>
@@ -2163,19 +2163,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>22/06/2026 00:00</t>
+          <t>23/06/2026 02:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uruguay - Cape Verde Islands</t>
+          <t>Norway - Senegal</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>1.2</v>
@@ -2318,19 +2318,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>22/06/2026 03:00</t>
+          <t>23/06/2026 05:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New Zealand - Egypt</t>
+          <t>Jordan - Algeria</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>1.2</v>
@@ -2473,19 +2473,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>22/06/2026 19:00</t>
+          <t>23/06/2026 19:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina - Austria</t>
+          <t>Portugal - Uzbekistan</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>1.2</v>
@@ -2628,19 +2628,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>22/06/2026 23:00</t>
+          <t>23/06/2026 22:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France - Iraq</t>
+          <t>England - Ghana</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
         <v>1.2</v>
@@ -2783,16 +2783,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>23/06/2026 02:00</t>
+          <t>24/06/2026 01:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway - Senegal</t>
+          <t>Panama - Croatia</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -2938,19 +2938,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>23/06/2026 05:00</t>
+          <t>24/06/2026 04:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan - Algeria</t>
+          <t>Colombia - Congo DR</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>1.2</v>
@@ -3093,19 +3093,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>23/06/2026 19:00</t>
+          <t>24/06/2026 21:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal - Uzbekistan</t>
+          <t>Switzerland - Canada</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F18" t="n">
         <v>1.2</v>
@@ -3248,19 +3248,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>23/06/2026 22:00</t>
+          <t>24/06/2026 21:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England - Ghana</t>
+          <t>Bosnia-Herzegovina - Qatar</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
         <v>1.2</v>
@@ -3403,16 +3403,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>24/06/2026 01:00</t>
+          <t>25/06/2026 00:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Panama - Croatia</t>
+          <t>Morocco - Haiti</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -3545,6 +3545,161 @@
         </is>
       </c>
       <c r="AI20" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>25/06/2026 00:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Scotland - Brazil</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>NOGOAL</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1X+UNDER</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>NON ANCORA REALE/DA VALIDARE</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Non Disponibile</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>

--- a/Storico_Validato_Betting.xlsx
+++ b/Storico_Validato_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI21"/>
+  <dimension ref="A1:AI20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,16 +613,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20/06/2026 19:00</t>
+          <t>20/06/2026 22:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Netherlands - Sweden</t>
+          <t>Germany - Ivory Coast</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
@@ -768,19 +768,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20/06/2026 22:00</t>
+          <t>21/06/2026 02:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Germany - Ivory Coast</t>
+          <t>Ecuador - Curaçao</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>1.2</v>
@@ -923,19 +923,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21/06/2026 02:00</t>
+          <t>21/06/2026 06:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ecuador - Curaçao</t>
+          <t>Tunisia - Japan</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>1.2</v>
@@ -1078,16 +1078,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21/06/2026 06:00</t>
+          <t>21/06/2026 18:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia - Japan</t>
+          <t>Spain - Saudi Arabia</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21/06/2026 18:00</t>
+          <t>21/06/2026 21:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain - Saudi Arabia</t>
+          <t>Belgium - Iran</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21/06/2026 21:00</t>
+          <t>22/06/2026 00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Belgium - Iran</t>
+          <t>Uruguay - Cape Verde Islands</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22/06/2026 00:00</t>
+          <t>22/06/2026 03:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uruguay - Cape Verde Islands</t>
+          <t>New Zealand - Egypt</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1698,19 +1698,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22/06/2026 03:00</t>
+          <t>22/06/2026 19:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New Zealand - Egypt</t>
+          <t>Argentina - Austria</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>1.2</v>
@@ -1853,19 +1853,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22/06/2026 19:00</t>
+          <t>22/06/2026 23:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Argentina - Austria</t>
+          <t>France - Iraq</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>1.2</v>
@@ -2008,12 +2008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>22/06/2026 23:00</t>
+          <t>23/06/2026 02:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>France - Iraq</t>
+          <t>Norway - Senegal</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -2163,16 +2163,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23/06/2026 02:00</t>
+          <t>23/06/2026 05:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway - Senegal</t>
+          <t>Jordan - Algeria</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -2318,16 +2318,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23/06/2026 05:00</t>
+          <t>23/06/2026 19:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan - Algeria</t>
+          <t>Portugal - Uzbekistan</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -2473,19 +2473,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>23/06/2026 19:00</t>
+          <t>23/06/2026 22:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal - Uzbekistan</t>
+          <t>England - Ghana</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
         <v>1.2</v>
@@ -2628,19 +2628,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>23/06/2026 22:00</t>
+          <t>24/06/2026 01:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England - Ghana</t>
+          <t>Panama - Croatia</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>1.2</v>
@@ -2783,19 +2783,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24/06/2026 01:00</t>
+          <t>24/06/2026 04:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Panama - Croatia</t>
+          <t>Colombia - Congo DR</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>1.2</v>
@@ -2938,19 +2938,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>24/06/2026 04:00</t>
+          <t>24/06/2026 21:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Colombia - Congo DR</t>
+          <t>Switzerland - Canada</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
         <v>1.2</v>
@@ -3098,14 +3098,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Switzerland - Canada</t>
+          <t>Bosnia-Herzegovina - Qatar</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
         <v>1.2</v>
@@ -3248,19 +3248,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>24/06/2026 21:00</t>
+          <t>25/06/2026 00:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bosnia-Herzegovina - Qatar</t>
+          <t>Morocco - Haiti</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>1.2</v>
@@ -3408,14 +3408,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco - Haiti</t>
+          <t>Scotland - Brazil</t>
         </is>
       </c>
       <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
         <v>4</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>1.2</v>
@@ -3545,161 +3545,6 @@
         </is>
       </c>
       <c r="AI20" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>FIFA World Cup</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>25/06/2026 00:00</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Scotland - Brazil</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>3</v>
-      </c>
-      <c r="E21" t="n">
-        <v>4</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>1X</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>OVER 1.5</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>UNDER 3.5</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>NOGOAL</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>1X+UNDER</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>

--- a/Storico_Validato_Betting.xlsx
+++ b/Storico_Validato_Betting.xlsx
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
         <v>1.2</v>

--- a/Storico_Validato_Betting.xlsx
+++ b/Storico_Validato_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI20"/>
+  <dimension ref="A1:AI19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,19 +613,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20/06/2026 22:00</t>
+          <t>21/06/2026 02:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Germany - Ivory Coast</t>
+          <t>Ecuador - Curaçao</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>1.2</v>
@@ -768,19 +768,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21/06/2026 02:00</t>
+          <t>21/06/2026 06:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ecuador - Curaçao</t>
+          <t>Tunisia - Japan</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1.2</v>
@@ -923,16 +923,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21/06/2026 06:00</t>
+          <t>21/06/2026 18:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia - Japan</t>
+          <t>Spain - Saudi Arabia</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21/06/2026 18:00</t>
+          <t>21/06/2026 21:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain - Saudi Arabia</t>
+          <t>Belgium - Iran</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21/06/2026 21:00</t>
+          <t>22/06/2026 00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Belgium - Iran</t>
+          <t>Uruguay - Cape Verde Islands</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22/06/2026 00:00</t>
+          <t>22/06/2026 03:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uruguay - Cape Verde Islands</t>
+          <t>New Zealand - Egypt</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1543,19 +1543,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22/06/2026 03:00</t>
+          <t>22/06/2026 19:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New Zealand - Egypt</t>
+          <t>Argentina - Austria</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
         <v>1.2</v>
@@ -1698,19 +1698,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22/06/2026 19:00</t>
+          <t>22/06/2026 23:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Argentina - Austria</t>
+          <t>France - Iraq</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>1.2</v>
@@ -1853,12 +1853,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22/06/2026 23:00</t>
+          <t>23/06/2026 02:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>France - Iraq</t>
+          <t>Norway - Senegal</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2008,16 +2008,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>23/06/2026 02:00</t>
+          <t>23/06/2026 05:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway - Senegal</t>
+          <t>Jordan - Algeria</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -2163,16 +2163,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23/06/2026 05:00</t>
+          <t>23/06/2026 19:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jordan - Algeria</t>
+          <t>Portugal - Uzbekistan</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -2318,19 +2318,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23/06/2026 19:00</t>
+          <t>23/06/2026 22:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal - Uzbekistan</t>
+          <t>England - Ghana</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
         <v>1.2</v>
@@ -2473,19 +2473,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>23/06/2026 22:00</t>
+          <t>24/06/2026 01:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England - Ghana</t>
+          <t>Panama - Croatia</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>1.2</v>
@@ -2628,19 +2628,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24/06/2026 01:00</t>
+          <t>24/06/2026 04:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Panama - Croatia</t>
+          <t>Colombia - Congo DR</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>1.2</v>
@@ -2783,19 +2783,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24/06/2026 04:00</t>
+          <t>24/06/2026 21:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Colombia - Congo DR</t>
+          <t>Switzerland - Canada</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
         <v>1.2</v>
@@ -2943,14 +2943,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Switzerland - Canada</t>
+          <t>Bosnia-Herzegovina - Qatar</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>1.2</v>
@@ -3093,19 +3093,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>24/06/2026 21:00</t>
+          <t>25/06/2026 00:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bosnia-Herzegovina - Qatar</t>
+          <t>Morocco - Haiti</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>1.2</v>
@@ -3253,14 +3253,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morocco - Haiti</t>
+          <t>Scotland - Brazil</t>
         </is>
       </c>
       <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
         <v>4</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>1.2</v>
@@ -3390,161 +3390,6 @@
         </is>
       </c>
       <c r="AI19" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>FIFA World Cup</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>25/06/2026 00:00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Scotland - Brazil</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>3</v>
-      </c>
-      <c r="E20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>1X</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>OVER 1.5</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>UNDER 3.5</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>NOGOAL</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>1X+UNDER</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>NON ANCORA REALE/DA VALIDARE</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Non Disponibile</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
         <is>
           <t>Non Disponibile</t>
         </is>
